--- a/stories/arbres/ATOM-SAN.HYG.003-07.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Anaïs est à table. La soupe est chaude. Son nez chatouille. Ça coule un peu. Maman est près d'elle. Maman tend un mouchoir. Anaïs prend le mouchoir. Elle se mouche. Atchoum, tout doux. Le nez est plus libre. Anaïs va à la poubelle. Elle jette le mouchoir. Maman dit : mouchoir, puis poubelle. Anaïs se lave les mains. L'eau est tiède. Elle revient. La soupe sent bon. Maman sourit. Anaïs reprend sa cuillère.</t>
+          <t>Anaïs est à table. La soupe est chaude. Son nez chatouille. Ça coule un peu. Maman est près d'elle. Maman tend un mouchoir. Anaïs prend le mouchoir. Elle se mouche. Atchoum, tout doux. Le nez est plus libre. Anaïs va à la poubelle. Elle jette le mouchoir. Mouchoir, puis poubelle. Anaïs se lave les mains. L'eau est tiède. Elle revient. La soupe sent bon. Maman sourit. Anaïs reprend sa cuillère.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Anaïs est à table. La soupe est chaude. Son nez chatouille. Ça coule un peu. Maman est près d'elle. Maman tend un mouchoir. Anaïs prend le mouchoir. Elle se mouche. Atchoum, tout doux. Le nez est plus libre. Anaïs va à la poubelle. Elle jette le mouchoir.
+maman|Mouchoir, puis poubelle.
+narrateur|Anaïs se lave les mains. L'eau est tiède. Elle revient. La soupe sent bon. Maman sourit. Anaïs reprend sa cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le nez d'Anaïs coule. Que prend-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Anaïs a pris un mouchoir. Elle s'est mouchée. Elle a jeté le mouchoir à la poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Anaïs finit sa soupe. Maman range le bol.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-07.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Anaïs se lave les mains. L'eau est tiède. Elle revient. La soupe sent bon. Maman sourit. Anaïs reprend sa cuillère.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Le nez d'Anaïs coule. Que prend-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Anaïs a pris un mouchoir. Elle s'est mouchée. Elle a jeté le mouchoir à la poubelle.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1837,7 @@
           <t>narrateur|Anaïs finit sa soupe. Maman range le bol.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.003-07.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Anaïs se mouche à table</t>
+          <t>Le rond de carotte</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.HYG.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un rond de carotte flotte. Nina tient sa cuillère. Son nez chatouille. Maman tend un mouchoir. Nina se mouche, jette, puis reprend la soupe.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Anaïs est à table. La soupe est chaude. Son nez chatouille. Ça coule un peu. Maman est près d'elle. Maman tend un mouchoir. Anaïs prend le mouchoir. Elle se mouche. Atchoum, tout doux. Le nez est plus libre. Anaïs va à la poubelle. Elle jette le mouchoir. Mouchoir, puis poubelle. Anaïs se lave les mains. L'eau est tiède. Elle revient. La soupe sent bon. Maman sourit. Anaïs reprend sa cuillère.</t>
+          <t>Un rond de carotte flotte. Il est orange. Il tourne tout doux. La cuillère en bois attend. La table est tiède. Une petite fumée monte. Elle touche le plafond. Ça sent la soupe. La nappe a des carreaux. En ce moment, Nina tient sa cuillère. La soupe est chaude. Son nez chatouille. Ça coule un peu. Maman. Ça chatouille. Tiens, Nina. Un mouchoir. Maman tend le mouchoir. Il est doux. Nina le prend. Elle se mouche. Atchoum, tout doux. Le nez est plus libre. Bravo, Nina. Tu as pris le mouchoir. On va à la poubelle ? Oui, maman. La poubelle est près de la porte. Nina jette le mouchoir. Toc. Mouchoir, puis poubelle. Mouchoir, puis poubelle. C'est du bon travail. Nina se lave les mains. L'eau est tiède. Elle essuie. Elle revient. La soupe sent bon. Tu reprends ta cuillère ? Oui. Nina reprend sa cuillère. Le rond de carotte attend. Elle le pousse tout doux. Il danse. Maman, il danse. Oui. Il danse dans le bol.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1329,60 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Anaïs est à table. La soupe est chaude. Son nez chatouille. Ça coule un peu. Maman est près d'elle. Maman tend un mouchoir. Anaïs prend le mouchoir. Elle se mouche. Atchoum, tout doux. Le nez est plus libre. Anaïs va à la poubelle. Elle jette le mouchoir.
+          <t>narrateur|Un rond de carotte flotte.
+narrateur|Il est orange.
+narrateur|Il tourne tout doux.
+narrateur|La cuillère en bois attend.
+narrateur|La table est tiède.
+narrateur|Une petite fumée monte.
+narrateur|Elle touche le plafond.
+narrateur|Ça sent la soupe.
+narrateur|La nappe a des carreaux.
+narrateur|En ce moment, Nina tient sa cuillère.
+narrateur|La soupe est chaude.
+narrateur|Son nez chatouille.
+narrateur|Ça coule un peu.
+enfant-f|Maman.
+enfant-f|Ça chatouille.
+maman|Tiens, Nina.
+maman|Un mouchoir.
+narrateur|Maman tend le mouchoir.
+narrateur|Il est doux.
+narrateur|Nina le prend.
+narrateur|Elle se mouche.
+narrateur|Atchoum, tout doux.
+narrateur|Le nez est plus libre.
+maman|Bravo, Nina.
+maman|Tu as pris le mouchoir.
+maman|On va à la poubelle ?
+enfant-f|Oui, maman.
+narrateur|La poubelle est près de la porte.
+narrateur|Nina jette le mouchoir.
+narrateur|Toc.
 maman|Mouchoir, puis poubelle.
-narrateur|Anaïs se lave les mains. L'eau est tiède. Elle revient. La soupe sent bon. Maman sourit. Anaïs reprend sa cuillère.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-f|Mouchoir, puis poubelle.
+maman|C'est du bon travail.
+narrateur|Nina se lave les mains.
+narrateur|L'eau est tiède.
+narrateur|Elle essuie.
+narrateur|Elle revient.
+narrateur|La soupe sent bon.
+maman|Tu reprends ta cuillère ?
+enfant-f|Oui.
+narrateur|Nina reprend sa cuillère.
+narrateur|Le rond de carotte attend.
+narrateur|Elle le pousse tout doux.
+narrateur|Il danse.
+enfant-f|Maman, il danse.
+maman|Oui.
+maman|Il danse dans le bol.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>cuillere,poubelle</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1407,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le nez d'Anaïs coule. Que prend-elle ?</t>
+          <t>Le nez de Nina coule. Que prend-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,7 +1563,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le nez d'Anaïs coule. Que prend-elle ?</t>
+          <t>narrateur|Le nez de Nina coule.
+narrateur|Que prend-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1526,7 +1592,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Anaïs a pris un mouchoir. Elle s'est mouchée. Elle a jeté le mouchoir à la poubelle.</t>
+          <t>Nina a pris un mouchoir. Elle s'est mouchée. Elle a jeté le mouchoir. Bravo. C'est du bon travail. Mouchoir, puis poubelle. Oui, maman. La soupe est encore chaude. Le rond orange tourne. Tu as fini ta cuillère ? Encore une. Nina goûte. C'est bon. La nappe est douce sous les mains.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,7 +1736,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Anaïs a pris un mouchoir. Elle s'est mouchée. Elle a jeté le mouchoir à la poubelle.</t>
+          <t>narrateur|Nina a pris un mouchoir.
+narrateur|Elle s'est mouchée.
+narrateur|Elle a jeté le mouchoir.
+maman|Bravo.
+maman|C'est du bon travail.
+maman|Mouchoir, puis poubelle.
+enfant-f|Oui, maman.
+narrateur|La soupe est encore chaude.
+narrateur|Le rond orange tourne.
+maman|Tu as fini ta cuillère ?
+enfant-f|Encore une.
+narrateur|Nina goûte.
+enfant-f|C'est bon.
+narrateur|La nappe est douce sous les mains.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1698,7 +1777,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Anaïs finit sa soupe. Maman range le bol.</t>
+          <t>Nina finit sa soupe. Maman range le bol. Le bol est chaud. Tu veux un peu d'eau ? Oui. Merci, maman. Nina boit une gorgée. La fumée s'en va. Le rond de carotte n'est plus là. On reste à table ? Oui. Nina reste assise. La cuisine est calme. Bravo, Nina. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1834,7 +1913,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Anaïs finit sa soupe. Maman range le bol.</t>
+          <t>narrateur|Nina finit sa soupe.
+narrateur|Maman range le bol.
+narrateur|Le bol est chaud.
+maman|Tu veux un peu d'eau ?
+enfant-f|Oui.
+enfant-f|Merci, maman.
+narrateur|Nina boit une gorgée.
+narrateur|La fumée s'en va.
+narrateur|Le rond de carotte n'est plus là.
+maman|On reste à table ?
+enfant-f|Oui.
+narrateur|Nina reste assise.
+narrateur|La cuisine est calme.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1862,7 +1955,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai pris un mouchoir. Puis la poubelle. Bravo. Tu as fait du bon travail. La soupe était bonne. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2002,7 +2095,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai pris un mouchoir.
+enfant-f|Puis la poubelle.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+maman|La soupe était bonne.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2024,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2160,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-07.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-07.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un rond de carotte flotte. Il est orange. Il tourne tout doux. La cuillère en bois attend. La table est tiède. Une petite fumée monte. Elle touche le plafond. Ça sent la soupe. La nappe a des carreaux. En ce moment, Nina tient sa cuillère. La soupe est chaude. Son nez chatouille. Ça coule un peu. Maman. Ça chatouille. Tiens, Nina. Un mouchoir. Maman tend le mouchoir. Il est doux. Nina le prend. Elle se mouche. Atchoum, tout doux. Le nez est plus libre. Bravo, Nina. Tu as pris le mouchoir. On va à la poubelle ? Oui, maman. La poubelle est près de la porte. Nina jette le mouchoir. Toc. Mouchoir, puis poubelle. Mouchoir, puis poubelle. C'est du bon travail. Nina se lave les mains. L'eau est tiède. Elle essuie. Elle revient. La soupe sent bon. Tu reprends ta cuillère ? Oui. Nina reprend sa cuillère. Le rond de carotte attend. Elle le pousse tout doux. Il danse. Maman, il danse. Oui. Il danse dans le bol.</t>
+          <t>Un rond de carotte flotte. Il est orange. Il tourne tout doux. La cuillère en bois attend. Elle est un peu humide. La table est tiède. Une petite fumée monte. Elle touche le plafond. Ça sent la soupe. La nappe a des carreaux. Un carreau rouge. Un carreau blanc. Un morceau de pain attend. Il est doré. En ce moment, Nina tient sa cuillère. La soupe est chaude. Son nez chatouille. Ça coule un peu. Maman. Ça chatouille. Tiens, Nina. Un mouchoir. Maman tend le mouchoir. Il est doux. Nina le prend. Elle se mouche. Atchoum, tout doux. Le nez est plus libre. Bravo, Nina. Tu as pris le mouchoir. On va à la poubelle ? Oui, maman. La poubelle est près de la porte. Nina marche tout doux. Elle jette le mouchoir. Toc. Mouchoir, puis poubelle. Mouchoir, puis poubelle. Tu as fini de jeter le mouchoir ? Oui. Nina se lave les mains. L'eau est tiède. Elle essuie. Elle revient. Elle s'assoit. La soupe sent bon. Tu reprends ta cuillère ? Oui. Nina reprend sa cuillère. Le rond de carotte attend. Elle le pousse tout doux. Il danse. Maman, il danse. Oui. Il danse dans le bol.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Anaïs est à table. La soupe est chaude. Son nez chatouille. Ça coule un peu. Maman est près d'elle. Maman tend un &lt;emphasis level="moderate"&gt;mouchoir&lt;/emphasis&gt;. Anaïs prend le mouchoir. Elle se mouche. Atchoum, tout doux. Le nez est plus libre. Anaïs va à la poubelle. Elle jette le mouchoir. Maman dit : mouchoir, puis poubelle. Anaïs se lave les mains. L'eau est tiède. Elle revient. La soupe sent bon. Maman sourit. Anaïs reprend sa cuillère.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un rond de carotte flotte. Il est orange. Il tourne tout doux. La cuillère en bois attend. Elle est un peu humide. La table est tiède. Une petite fumée monte. Elle touche le plafond. Ça sent la soupe. La nappe a des carreaux. Un carreau rouge. Un carreau blanc. Un morceau de pain attend. Il est doré. En ce moment, Nina tient sa cuillère. La soupe est chaude. Son nez chatouille. Ça coule un peu. Maman. Ça chatouille. Tiens, Nina. Un mouchoir. Maman tend le mouchoir. Il est doux. Nina le prend. Elle se mouche. Atchoum, tout doux. Le nez est plus libre. Bravo, Nina. Tu as pris le mouchoir. On va à la poubelle ? Oui, maman. La poubelle est près de la porte. Nina marche tout doux. Elle jette le mouchoir. Toc. Mouchoir, puis poubelle. Mouchoir, puis poubelle. Tu as fini de jeter le mouchoir ? Oui. Nina se lave les mains. L'eau est tiède. Elle essuie. Elle revient. Elle s'assoit. La soupe sent bon. Tu reprends ta cuillère ? Oui. Nina reprend sa cuillère. Le rond de carotte attend. Elle le pousse tout doux. Il danse. Maman, il danse. Oui. Il danse dans le bol.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1333,11 +1333,16 @@
 narrateur|Il est orange.
 narrateur|Il tourne tout doux.
 narrateur|La cuillère en bois attend.
+narrateur|Elle est un peu humide.
 narrateur|La table est tiède.
 narrateur|Une petite fumée monte.
 narrateur|Elle touche le plafond.
 narrateur|Ça sent la soupe.
 narrateur|La nappe a des carreaux.
+narrateur|Un carreau rouge.
+narrateur|Un carreau blanc.
+narrateur|Un morceau de pain attend.
+narrateur|Il est doré.
 narrateur|En ce moment, Nina tient sa cuillère.
 narrateur|La soupe est chaude.
 narrateur|Son nez chatouille.
@@ -1357,15 +1362,18 @@
 maman|On va à la poubelle ?
 enfant-f|Oui, maman.
 narrateur|La poubelle est près de la porte.
-narrateur|Nina jette le mouchoir.
+narrateur|Nina marche tout doux.
+narrateur|Elle jette le mouchoir.
 narrateur|Toc.
 maman|Mouchoir, puis poubelle.
 enfant-f|Mouchoir, puis poubelle.
-maman|C'est du bon travail.
+maman|Tu as fini de jeter le mouchoir ?
+enfant-f|Oui.
 narrateur|Nina se lave les mains.
 narrateur|L'eau est tiède.
 narrateur|Elle essuie.
 narrateur|Elle revient.
+narrateur|Elle s'assoit.
 narrateur|La soupe sent bon.
 maman|Tu reprends ta cuillère ?
 enfant-f|Oui.
@@ -1412,7 +1420,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le nez d'Anaïs coule. Que prend-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le nez de Nina coule. Que prend-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1567,7 +1575,6 @@
 narrateur|Que prend-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1592,12 +1599,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a pris un mouchoir. Elle s'est mouchée. Elle a jeté le mouchoir. Bravo. C'est du bon travail. Mouchoir, puis poubelle. Oui, maman. La soupe est encore chaude. Le rond orange tourne. Tu as fini ta cuillère ? Encore une. Nina goûte. C'est bon. La nappe est douce sous les mains.</t>
+          <t>Nina a pris un mouchoir. Elle s'est mouchée. Elle a jeté le mouchoir. Bravo. Mouchoir, puis poubelle. Oui, maman. La soupe est encore chaude. Le rond orange tourne. Tu as fini ta cuillère ? Encore une. Nina goûte. C'est bon. La nappe est douce sous les mains.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Anaïs a pris un &lt;emphasis level="moderate"&gt;mouchoir&lt;/emphasis&gt;. Elle s'est mouchée. Elle a jeté le mouchoir à la poubelle.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a pris un mouchoir. Elle s'est mouchée. Elle a jeté le mouchoir. Bravo. Mouchoir, puis poubelle. Oui, maman. La soupe est encore chaude. Le rond orange tourne. Tu as fini ta cuillère ? Encore une. Nina goûte. C'est bon. La nappe est douce sous les mains.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1740,7 +1747,6 @@
 narrateur|Elle s'est mouchée.
 narrateur|Elle a jeté le mouchoir.
 maman|Bravo.
-maman|C'est du bon travail.
 maman|Mouchoir, puis poubelle.
 enfant-f|Oui, maman.
 narrateur|La soupe est encore chaude.
@@ -1752,7 +1758,6 @@
 narrateur|La nappe est douce sous les mains.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1777,12 +1782,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nina finit sa soupe. Maman range le bol. Le bol est chaud. Tu veux un peu d'eau ? Oui. Merci, maman. Nina boit une gorgée. La fumée s'en va. Le rond de carotte n'est plus là. On reste à table ? Oui. Nina reste assise. La cuisine est calme. Bravo, Nina. Tu as fait du bon travail.</t>
+          <t>Nina finit sa soupe. Maman range le bol. Le bol est chaud. Tu veux un peu d'eau ? Oui. Merci, maman. Nina boit une gorgée. La fumée s'en va. Le rond de carotte n'est plus là. Le pain doré aussi. On reste à table ? Oui. Nina reste assise. La nappe est douce. La cuisine est calme. Bravo, Nina. Tu as repris ta cuillère. C'était bon. Un carreau rouge reste sous la main. Tu es encore bien assise. Oui, maman. La cuillère en bois attend, propre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Anaïs finit sa soupe. Maman range le bol.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina finit sa soupe. Maman range le bol. Le bol est chaud. Tu veux un peu d'eau ? Oui. Merci, maman. Nina boit une gorgée. La fumée s'en va. Le rond de carotte n'est plus là. Le pain doré aussi. On reste à table ? Oui. Nina reste assise. La nappe est douce. La cuisine est calme. Bravo, Nina. Tu as repris ta cuillère. C'était bon. Un carreau rouge reste sous la main. Tu es encore bien assise. Oui, maman. La cuillère en bois attend, propre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1922,15 +1927,21 @@
 narrateur|Nina boit une gorgée.
 narrateur|La fumée s'en va.
 narrateur|Le rond de carotte n'est plus là.
+narrateur|Le pain doré aussi.
 maman|On reste à table ?
 enfant-f|Oui.
 narrateur|Nina reste assise.
+narrateur|La nappe est douce.
 narrateur|La cuisine est calme.
 maman|Bravo, Nina.
-maman|Tu as fait du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+maman|Tu as repris ta cuillère.
+enfant-f|C'était bon.
+narrateur|Un carreau rouge reste sous la main.
+maman|Tu es encore bien assise.
+enfant-f|Oui, maman.
+narrateur|La cuillère en bois attend, propre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1955,12 +1966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai pris un mouchoir. Puis la poubelle. Bravo. Tu as fait du bon travail. La soupe était bonne. L'histoire est finie.</t>
+          <t>J'ai pris un mouchoir. Puis la poubelle. Bravo. La soupe était bonne.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai pris un mouchoir. Puis la poubelle. Bravo. La soupe était bonne.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2098,12 +2109,9 @@
           <t>enfant-f|J'ai pris un mouchoir.
 enfant-f|Puis la poubelle.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-maman|La soupe était bonne.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|La soupe était bonne.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2122,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2167,6 +2175,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-07.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-07.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Anaïs, maman</t>
+          <t>Nina, maman</t>
         </is>
       </c>
     </row>
